--- a/bitcoin_trades.xlsx
+++ b/bitcoin_trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,51 @@
         <is>
           <t>Balance</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10EMA_Trend_5m</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:32:23</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>76838.2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:48:01</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>76816.89999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.06920105845288134</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>75</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>99.78591198593136</v>
       </c>
     </row>
   </sheetData>

--- a/bitcoin_trades.xlsx
+++ b/bitcoin_trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,6 +516,51 @@
       </c>
       <c r="K2" t="n">
         <v>99.78591198593136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5EMA_Reversal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:48:01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>76816.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-24 12:48:44</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>76856.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.1295764041276804</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>99.65633558180369</v>
       </c>
     </row>
   </sheetData>

--- a/bitcoin_trades.xlsx
+++ b/bitcoin_trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,6 +561,51 @@
       </c>
       <c r="K3" t="n">
         <v>99.65633558180369</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5EMA_Reversal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-24 12:48:44</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>76902.39999999999</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-24 14:29:23</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>76810.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2977285897438565</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Price closed above 20 EMA</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>99.95406417154754</v>
       </c>
     </row>
   </sheetData>
